--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34596,6 +34596,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1489" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1489" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34619,6 +34619,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1490" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34642,6 +34642,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1491" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34665,6 +34665,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1492" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1492" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34529,7 +34529,7 @@
     </row>
     <row r="1486">
       <c r="A1486" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1486" t="n">
         <v>0</v>
@@ -34552,7 +34552,7 @@
     </row>
     <row r="1487">
       <c r="A1487" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1487" t="n">
         <v>0</v>
@@ -34575,7 +34575,7 @@
     </row>
     <row r="1488">
       <c r="A1488" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1488" t="n">
         <v>0</v>
@@ -34598,7 +34598,7 @@
     </row>
     <row r="1489">
       <c r="A1489" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1489" t="n">
         <v>0</v>
@@ -34621,7 +34621,7 @@
     </row>
     <row r="1490">
       <c r="A1490" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1490" t="n">
         <v>0</v>
@@ -34644,7 +34644,7 @@
     </row>
     <row r="1491">
       <c r="A1491" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1491" t="n">
         <v>0</v>
@@ -34667,7 +34667,7 @@
     </row>
     <row r="1492">
       <c r="A1492" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1492" t="n">
         <v>0</v>
@@ -34685,6 +34685,29 @@
         <v>0.381999999284744</v>
       </c>
       <c r="G1492" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1493" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1493" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34711,6 +34711,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1494">
+      <c r="A1494" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1494" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1494" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1494" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1495" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1495" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1495" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1495" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34757,6 +34757,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1496" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34780,6 +34780,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1497" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34803,6 +34803,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1498">
+      <c r="A1498" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1498" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34826,6 +34826,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1499">
+      <c r="A1499" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1499" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34849,6 +34849,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1500">
+      <c r="A1500" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1500" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1500" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34872,6 +34872,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1501">
+      <c r="A1501" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1501" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1501" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34895,6 +34895,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1502">
+      <c r="A1502" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1502" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34918,6 +34918,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1503">
+      <c r="A1503" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1503" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34941,6 +34941,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1504">
+      <c r="A1504" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1504" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34964,6 +34964,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1505">
+      <c r="A1505" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1505" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -34987,6 +34987,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1506">
+      <c r="A1506" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1506" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35010,6 +35010,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1507">
+      <c r="A1507" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1507" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35033,6 +35033,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1508">
+      <c r="A1508" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1508" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1508" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1508" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35056,6 +35056,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1509">
+      <c r="A1509" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1509" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1509" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1509" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35102,6 +35102,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1511">
+      <c r="A1511" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1511" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1511" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1511" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35125,6 +35125,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1512">
+      <c r="A1512" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1512" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1512" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1512" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35148,6 +35148,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1513">
+      <c r="A1513" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1513" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1513" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1513" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -35171,6 +35171,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1514">
+      <c r="A1514" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1514" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1514" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1514" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44313,6 +44313,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1516">
+      <c r="A1516" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1516" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1516" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1516" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1516" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1516" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44342,6 +44342,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1517">
+      <c r="A1517" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1517" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1517" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1517" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1517" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1517" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44371,6 +44371,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1518">
+      <c r="A1518" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1518" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1518" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1518" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1518" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1518" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44400,6 +44400,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1519">
+      <c r="A1519" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1519" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1519" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1519" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1519" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1519" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44429,6 +44429,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1520">
+      <c r="A1520" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1520" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1520" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1520" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1520" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1520" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44458,6 +44458,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1521">
+      <c r="A1521" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1521" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1521" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1521" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1521" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1521" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44487,6 +44487,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1522">
+      <c r="A1522" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1522" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1522" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1522" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1522" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1522" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44516,6 +44516,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1523">
+      <c r="A1523" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1523" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1523" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1523" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1523" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1523" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OSA.MI.xlsx
+++ b/data/OSA.MI.xlsx
@@ -44545,6 +44545,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1524">
+      <c r="A1524" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1524" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1524" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="D1524" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="G1524" t="n">
+        <v>0.381999999284744</v>
+      </c>
+      <c r="H1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1524" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
